--- a/UDS_Diagnostic_Questionnaire/J02/UDS_Diagnostic_Questionnaire_J02.xlsx
+++ b/UDS_Diagnostic_Questionnaire/J02/UDS_Diagnostic_Questionnaire_J02.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11925" activeTab="7"/>
+    <workbookView windowWidth="28800" windowHeight="11925" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="History" sheetId="1" r:id="rId1"/>

--- a/UDS_Diagnostic_Questionnaire/J02/UDS_Diagnostic_Questionnaire_J02.xlsx
+++ b/UDS_Diagnostic_Questionnaire/J02/UDS_Diagnostic_Questionnaire_J02.xlsx
@@ -18,8 +18,8 @@
     <sheet name="DID List" sheetId="4" r:id="rId4"/>
     <sheet name="RID List" sheetId="5" r:id="rId5"/>
     <sheet name="NVM List" sheetId="6" r:id="rId6"/>
-    <sheet name="DcmDspSecurity" sheetId="9" r:id="rId7"/>
-    <sheet name="DcmDspSession" sheetId="10" r:id="rId8"/>
+    <sheet name="DcmDspSecurity" sheetId="7" r:id="rId7"/>
+    <sheet name="DcmDspSession" sheetId="8" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'RID List'!$A$2:$P$32</definedName>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1199" uniqueCount="403">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1199" uniqueCount="402">
   <si>
     <t>History</t>
   </si>
@@ -74,6 +74,15 @@
     <t>Initialized from FAWVW_UDS_Diagnostic_Questionnaire_MFK_DK3_J02_V001_260920: General(48) + Service(14 svc/29 rows, NRC22) + DID(22, unlock 22:2E format) + RID(2 RIDs/4 rows: 8510/8511, 其余为客户示例) + NVM(5)</t>
   </si>
   <si>
+    <t>V1.1</t>
+  </si>
+  <si>
+    <t>2026-09-29</t>
+  </si>
+  <si>
+    <t>Per FAW-VW Diagnostic Access Safety Protection 2.0: DcmDspSecurity 27 service unlock level Boot 9-&gt;2 (App L1 / Develop L49 unchanged), App &amp; Boot SeedSize/KeySize 2/4 -&gt; 12/12 bytes; added SecurityAccess_27_J02.json</t>
+  </si>
+  <si>
     <t>General</t>
   </si>
   <si>
@@ -1184,40 +1193,28 @@
     <t>DcmRbDspSecurityRowUseFlexibleLength</t>
   </si>
   <si>
-    <t>Unlocked_L3</t>
+    <t>Unlocked_Boot</t>
   </si>
   <si>
     <t>BootSecurityCompareKey</t>
   </si>
   <si>
-    <t>BootSecurityGetAttempCount</t>
-  </si>
-  <si>
     <t>BootSecurityGetSeed</t>
   </si>
   <si>
-    <t>BootSecuritySetAttempCount</t>
-  </si>
-  <si>
     <t>USE_ASYNCH_FNC</t>
   </si>
   <si>
-    <t>Unlocked_L1</t>
+    <t>Unlocked_App</t>
   </si>
   <si>
     <t>AppSecurityCompareKey</t>
   </si>
   <si>
-    <t>AppSecurityGetAttempCount</t>
-  </si>
-  <si>
     <t>AppSecurityGetSeed</t>
   </si>
   <si>
-    <t>AppSecuritySetAttempCount</t>
-  </si>
-  <si>
-    <t>Unlocked_L49</t>
+    <t>Unlocked_Develop</t>
   </si>
   <si>
     <t>DevelopSecurityCompareKey</t>
@@ -1264,7 +1261,7 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1322,13 +1319,6 @@
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -1856,152 +1846,152 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="5">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="9">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="10">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="11">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="12">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="34" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="35" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="36" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2048,13 +2038,12 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -2465,204 +2454,212 @@
       <c r="E3" s="11"/>
     </row>
     <row r="4" ht="18.75" customHeight="1" spans="1:5">
-      <c r="A4" s="11"/>
-      <c r="B4" s="24"/>
-      <c r="C4" s="11"/>
-      <c r="D4" s="11"/>
+      <c r="A4" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>12</v>
+      </c>
       <c r="E4" s="11"/>
     </row>
     <row r="5" ht="18.75" customHeight="1" spans="1:5">
       <c r="A5" s="11"/>
-      <c r="B5" s="24"/>
+      <c r="B5" s="23"/>
       <c r="C5" s="11"/>
       <c r="D5" s="11"/>
       <c r="E5" s="11"/>
     </row>
     <row r="6" ht="18.75" customHeight="1" spans="1:5">
       <c r="A6" s="11"/>
-      <c r="B6" s="24"/>
+      <c r="B6" s="23"/>
       <c r="C6" s="11"/>
       <c r="D6" s="11"/>
       <c r="E6" s="11"/>
     </row>
     <row r="7" ht="18.75" customHeight="1" spans="1:5">
       <c r="A7" s="11"/>
-      <c r="B7" s="24"/>
+      <c r="B7" s="23"/>
       <c r="C7" s="11"/>
       <c r="D7" s="11"/>
       <c r="E7" s="11"/>
     </row>
     <row r="8" ht="18.75" customHeight="1" spans="1:5">
       <c r="A8" s="11"/>
-      <c r="B8" s="24"/>
+      <c r="B8" s="23"/>
       <c r="C8" s="11"/>
       <c r="D8" s="11"/>
       <c r="E8" s="11"/>
     </row>
     <row r="9" ht="18.75" customHeight="1" spans="1:5">
       <c r="A9" s="11"/>
-      <c r="B9" s="24"/>
+      <c r="B9" s="23"/>
       <c r="C9" s="11"/>
       <c r="D9" s="11"/>
       <c r="E9" s="11"/>
     </row>
     <row r="10" ht="18.75" customHeight="1" spans="1:5">
       <c r="A10" s="11"/>
-      <c r="B10" s="24"/>
+      <c r="B10" s="23"/>
       <c r="C10" s="11"/>
       <c r="D10" s="11"/>
       <c r="E10" s="11"/>
     </row>
     <row r="11" ht="18.75" customHeight="1" spans="1:5">
       <c r="A11" s="11"/>
-      <c r="B11" s="24"/>
+      <c r="B11" s="23"/>
       <c r="C11" s="11"/>
       <c r="D11" s="11"/>
       <c r="E11" s="11"/>
     </row>
     <row r="12" ht="18.75" customHeight="1" spans="1:5">
       <c r="A12" s="11"/>
-      <c r="B12" s="24"/>
+      <c r="B12" s="23"/>
       <c r="C12" s="11"/>
       <c r="D12" s="11"/>
       <c r="E12" s="11"/>
     </row>
     <row r="13" ht="18.75" customHeight="1" spans="1:5">
       <c r="A13" s="11"/>
-      <c r="B13" s="24"/>
+      <c r="B13" s="23"/>
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
       <c r="E13" s="11"/>
     </row>
     <row r="14" ht="18.75" customHeight="1" spans="1:5">
       <c r="A14" s="11"/>
-      <c r="B14" s="24"/>
+      <c r="B14" s="23"/>
       <c r="C14" s="11"/>
       <c r="D14" s="11"/>
       <c r="E14" s="11"/>
     </row>
     <row r="15" ht="18.75" customHeight="1" spans="1:5">
       <c r="A15" s="11"/>
-      <c r="B15" s="24"/>
+      <c r="B15" s="23"/>
       <c r="C15" s="11"/>
       <c r="D15" s="11"/>
       <c r="E15" s="11"/>
     </row>
     <row r="16" ht="18.75" customHeight="1" spans="1:5">
       <c r="A16" s="11"/>
-      <c r="B16" s="24"/>
+      <c r="B16" s="23"/>
       <c r="C16" s="11"/>
       <c r="D16" s="11"/>
       <c r="E16" s="11"/>
     </row>
     <row r="17" ht="18.75" customHeight="1" spans="1:5">
       <c r="A17" s="11"/>
-      <c r="B17" s="24"/>
+      <c r="B17" s="23"/>
       <c r="C17" s="11"/>
       <c r="D17" s="11"/>
       <c r="E17" s="11"/>
     </row>
     <row r="18" ht="18.75" customHeight="1" spans="1:5">
       <c r="A18" s="11"/>
-      <c r="B18" s="24"/>
+      <c r="B18" s="23"/>
       <c r="C18" s="11"/>
       <c r="D18" s="11"/>
       <c r="E18" s="11"/>
     </row>
     <row r="19" ht="18.75" customHeight="1" spans="1:5">
       <c r="A19" s="11"/>
-      <c r="B19" s="24"/>
+      <c r="B19" s="23"/>
       <c r="C19" s="11"/>
       <c r="D19" s="11"/>
       <c r="E19" s="11"/>
     </row>
     <row r="20" ht="18.75" customHeight="1" spans="1:5">
       <c r="A20" s="11"/>
-      <c r="B20" s="24"/>
+      <c r="B20" s="23"/>
       <c r="C20" s="11"/>
       <c r="D20" s="11"/>
       <c r="E20" s="11"/>
     </row>
     <row r="21" ht="18.75" customHeight="1" spans="1:5">
       <c r="A21" s="11"/>
-      <c r="B21" s="24"/>
+      <c r="B21" s="23"/>
       <c r="C21" s="11"/>
       <c r="D21" s="11"/>
       <c r="E21" s="11"/>
     </row>
     <row r="22" ht="18.75" customHeight="1" spans="1:5">
       <c r="A22" s="11"/>
-      <c r="B22" s="24"/>
+      <c r="B22" s="23"/>
       <c r="C22" s="11"/>
       <c r="D22" s="11"/>
       <c r="E22" s="11"/>
     </row>
     <row r="23" ht="18.75" customHeight="1" spans="1:5">
       <c r="A23" s="11"/>
-      <c r="B23" s="24"/>
+      <c r="B23" s="23"/>
       <c r="C23" s="11"/>
       <c r="D23" s="11"/>
       <c r="E23" s="11"/>
     </row>
     <row r="24" ht="18.75" customHeight="1" spans="1:5">
       <c r="A24" s="11"/>
-      <c r="B24" s="24"/>
+      <c r="B24" s="23"/>
       <c r="C24" s="11"/>
       <c r="D24" s="11"/>
       <c r="E24" s="11"/>
     </row>
     <row r="25" ht="18.75" customHeight="1" spans="1:5">
       <c r="A25" s="11"/>
-      <c r="B25" s="24"/>
+      <c r="B25" s="23"/>
       <c r="C25" s="11"/>
       <c r="D25" s="11"/>
       <c r="E25" s="11"/>
     </row>
     <row r="26" ht="18.75" customHeight="1" spans="1:5">
       <c r="A26" s="11"/>
-      <c r="B26" s="24"/>
+      <c r="B26" s="23"/>
       <c r="C26" s="11"/>
       <c r="D26" s="11"/>
       <c r="E26" s="11"/>
     </row>
     <row r="27" ht="18.75" customHeight="1" spans="1:5">
       <c r="A27" s="11"/>
-      <c r="B27" s="24"/>
+      <c r="B27" s="23"/>
       <c r="C27" s="11"/>
       <c r="D27" s="11"/>
       <c r="E27" s="11"/>
     </row>
     <row r="28" ht="18.75" customHeight="1" spans="1:5">
       <c r="A28" s="11"/>
-      <c r="B28" s="24"/>
+      <c r="B28" s="23"/>
       <c r="C28" s="11"/>
       <c r="D28" s="11"/>
       <c r="E28" s="11"/>
     </row>
     <row r="29" ht="18.75" customHeight="1" spans="1:5">
       <c r="A29" s="11"/>
-      <c r="B29" s="24"/>
+      <c r="B29" s="23"/>
       <c r="C29" s="11"/>
       <c r="D29" s="11"/>
       <c r="E29" s="11"/>
     </row>
     <row r="30" ht="18.75" customHeight="1" spans="1:5">
       <c r="A30" s="11"/>
-      <c r="B30" s="24"/>
+      <c r="B30" s="23"/>
       <c r="C30" s="11"/>
       <c r="D30" s="11"/>
       <c r="E30" s="11"/>
     </row>
     <row r="31" ht="18.75" customHeight="1" spans="1:5">
       <c r="A31" s="11"/>
-      <c r="B31" s="24"/>
+      <c r="B31" s="23"/>
       <c r="C31" s="11"/>
       <c r="D31" s="11"/>
       <c r="E31" s="11"/>
     </row>
     <row r="32" ht="18.75" customHeight="1" spans="1:5">
       <c r="A32" s="11"/>
-      <c r="B32" s="24"/>
+      <c r="B32" s="23"/>
       <c r="C32" s="11"/>
       <c r="D32" s="11"/>
       <c r="E32" s="11"/>
@@ -2684,577 +2681,577 @@
   <dimension ref="A1:E50"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="24.0083333333333" style="18" customWidth="1"/>
-    <col min="2" max="2" width="20.0083333333333" style="18" customWidth="1"/>
-    <col min="3" max="3" width="38.0083333333333" style="19" customWidth="1"/>
-    <col min="4" max="5" width="24.0083333333333" style="19" customWidth="1"/>
+    <col min="1" max="1" width="24.0083333333333" customWidth="1"/>
+    <col min="2" max="2" width="20.0083333333333" customWidth="1"/>
+    <col min="3" max="3" width="38.0083333333333" style="18" customWidth="1"/>
+    <col min="4" max="5" width="24.0083333333333" style="18" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.75" customHeight="1" spans="1:5">
       <c r="A1" s="13" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" s="4" customFormat="1" ht="30" customHeight="1" spans="1:5">
       <c r="A2" s="9" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" s="4" customFormat="1" ht="18.75" customHeight="1" spans="1:5">
-      <c r="A3" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" s="20" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3" s="21" t="s">
+      <c r="A3" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="E3" s="21"/>
+      <c r="B3" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" s="20"/>
     </row>
     <row r="4" ht="18.75" customHeight="1" spans="1:5">
-      <c r="A4" s="22"/>
-      <c r="B4" s="22"/>
-      <c r="C4" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="D4" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="E4" s="21"/>
+      <c r="A4" s="21"/>
+      <c r="B4" s="21"/>
+      <c r="C4" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" s="20"/>
     </row>
     <row r="5" ht="18.75" customHeight="1" spans="1:5">
-      <c r="A5" s="22"/>
-      <c r="B5" s="22"/>
-      <c r="C5" s="21" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5" s="21"/>
+      <c r="A5" s="21"/>
+      <c r="B5" s="21"/>
+      <c r="C5" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" s="20"/>
     </row>
     <row r="6" ht="18.75" customHeight="1" spans="1:5">
-      <c r="A6" s="22"/>
-      <c r="B6" s="22"/>
-      <c r="C6" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" s="21" t="s">
-        <v>25</v>
-      </c>
-      <c r="E6" s="21"/>
+      <c r="A6" s="21"/>
+      <c r="B6" s="21"/>
+      <c r="C6" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="E6" s="20"/>
     </row>
     <row r="7" ht="18.75" customHeight="1" spans="1:5">
-      <c r="A7" s="22"/>
-      <c r="B7" s="22"/>
-      <c r="C7" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="D7" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="E7" s="21"/>
+      <c r="A7" s="21"/>
+      <c r="B7" s="21"/>
+      <c r="C7" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7" s="20"/>
     </row>
     <row r="8" ht="18.75" customHeight="1" spans="1:5">
-      <c r="A8" s="22"/>
-      <c r="B8" s="22"/>
-      <c r="C8" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="D8" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="E8" s="21"/>
+      <c r="A8" s="21"/>
+      <c r="B8" s="21"/>
+      <c r="C8" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="E8" s="20"/>
     </row>
     <row r="9" ht="18.75" customHeight="1" spans="1:5">
-      <c r="A9" s="22"/>
-      <c r="B9" s="22"/>
-      <c r="C9" s="21" t="s">
-        <v>30</v>
-      </c>
-      <c r="D9" s="21" t="s">
-        <v>31</v>
-      </c>
-      <c r="E9" s="21"/>
+      <c r="A9" s="21"/>
+      <c r="B9" s="21"/>
+      <c r="C9" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="E9" s="20"/>
     </row>
     <row r="10" ht="18.75" customHeight="1" spans="1:5">
-      <c r="A10" s="22"/>
-      <c r="B10" s="22"/>
-      <c r="C10" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="D10" s="21" t="s">
-        <v>33</v>
-      </c>
-      <c r="E10" s="21"/>
+      <c r="A10" s="21"/>
+      <c r="B10" s="21"/>
+      <c r="C10" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="E10" s="20"/>
     </row>
     <row r="11" ht="18.75" customHeight="1" spans="1:5">
-      <c r="A11" s="22"/>
-      <c r="B11" s="23"/>
-      <c r="C11" s="21" t="s">
-        <v>34</v>
-      </c>
-      <c r="D11" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="E11" s="21"/>
+      <c r="A11" s="21"/>
+      <c r="B11" s="22"/>
+      <c r="C11" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="D11" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="E11" s="20"/>
     </row>
     <row r="12" ht="18.75" customHeight="1" spans="1:5">
-      <c r="A12" s="22"/>
-      <c r="B12" s="20" t="s">
-        <v>36</v>
-      </c>
-      <c r="C12" s="21" t="s">
-        <v>37</v>
-      </c>
-      <c r="D12" s="21" t="s">
-        <v>38</v>
-      </c>
-      <c r="E12" s="21"/>
+      <c r="A12" s="21"/>
+      <c r="B12" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="C12" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="D12" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="E12" s="20"/>
     </row>
     <row r="13" ht="18.75" customHeight="1" spans="1:5">
-      <c r="A13" s="22"/>
-      <c r="B13" s="22"/>
-      <c r="C13" s="21" t="s">
-        <v>39</v>
-      </c>
-      <c r="D13" s="21" t="s">
-        <v>40</v>
-      </c>
-      <c r="E13" s="21"/>
+      <c r="A13" s="21"/>
+      <c r="B13" s="21"/>
+      <c r="C13" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="D13" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="E13" s="20"/>
     </row>
     <row r="14" ht="18.75" customHeight="1" spans="1:5">
-      <c r="A14" s="22"/>
-      <c r="B14" s="22"/>
-      <c r="C14" s="21" t="s">
-        <v>41</v>
-      </c>
-      <c r="D14" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="E14" s="21"/>
+      <c r="A14" s="21"/>
+      <c r="B14" s="21"/>
+      <c r="C14" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="D14" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="E14" s="20"/>
     </row>
     <row r="15" ht="18.75" customHeight="1" spans="1:5">
-      <c r="A15" s="22"/>
-      <c r="B15" s="22"/>
-      <c r="C15" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="D15" s="21" t="s">
-        <v>44</v>
-      </c>
-      <c r="E15" s="21"/>
+      <c r="A15" s="21"/>
+      <c r="B15" s="21"/>
+      <c r="C15" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="D15" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="E15" s="20"/>
     </row>
     <row r="16" ht="18.75" customHeight="1" spans="1:5">
-      <c r="A16" s="23"/>
-      <c r="B16" s="23"/>
-      <c r="C16" s="21" t="s">
-        <v>45</v>
-      </c>
-      <c r="D16" s="21" t="s">
-        <v>46</v>
-      </c>
-      <c r="E16" s="21"/>
+      <c r="A16" s="22"/>
+      <c r="B16" s="22"/>
+      <c r="C16" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="D16" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="E16" s="20"/>
     </row>
     <row r="17" s="4" customFormat="1" ht="18.75" customHeight="1" spans="1:5">
-      <c r="A17" s="20" t="s">
-        <v>47</v>
-      </c>
-      <c r="B17" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="C17" s="21" t="s">
-        <v>49</v>
-      </c>
-      <c r="D17" s="21" t="s">
+      <c r="A17" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="E17" s="21"/>
+      <c r="B17" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="C17" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="D17" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="E17" s="20"/>
     </row>
     <row r="18" ht="18.75" customHeight="1" spans="1:5">
-      <c r="A18" s="22"/>
-      <c r="B18" s="22"/>
-      <c r="C18" s="21" t="s">
-        <v>51</v>
-      </c>
-      <c r="D18" s="21" t="s">
-        <v>52</v>
-      </c>
-      <c r="E18" s="21"/>
+      <c r="A18" s="21"/>
+      <c r="B18" s="21"/>
+      <c r="C18" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="D18" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="E18" s="20"/>
     </row>
     <row r="19" ht="18.75" customHeight="1" spans="1:5">
-      <c r="A19" s="22"/>
-      <c r="B19" s="22"/>
-      <c r="C19" s="21" t="s">
-        <v>53</v>
-      </c>
-      <c r="D19" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="E19" s="21"/>
+      <c r="A19" s="21"/>
+      <c r="B19" s="21"/>
+      <c r="C19" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="D19" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="E19" s="20"/>
     </row>
     <row r="20" ht="18.75" customHeight="1" spans="1:5">
-      <c r="A20" s="22"/>
-      <c r="B20" s="22"/>
-      <c r="C20" s="21" t="s">
+      <c r="A20" s="21"/>
+      <c r="B20" s="21"/>
+      <c r="C20" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="D20" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="D20" s="21" t="s">
-        <v>52</v>
-      </c>
-      <c r="E20" s="21"/>
+      <c r="E20" s="20"/>
     </row>
     <row r="21" ht="18.75" customHeight="1" spans="1:5">
-      <c r="A21" s="22"/>
-      <c r="B21" s="22"/>
-      <c r="C21" s="21" t="s">
-        <v>56</v>
-      </c>
-      <c r="D21" s="21" t="s">
-        <v>57</v>
-      </c>
-      <c r="E21" s="21"/>
+      <c r="A21" s="21"/>
+      <c r="B21" s="21"/>
+      <c r="C21" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="D21" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="E21" s="20"/>
     </row>
     <row r="22" ht="18.75" customHeight="1" spans="1:5">
-      <c r="A22" s="22"/>
-      <c r="B22" s="22"/>
-      <c r="C22" s="21" t="s">
-        <v>58</v>
-      </c>
-      <c r="D22" s="21" t="s">
-        <v>59</v>
-      </c>
-      <c r="E22" s="21"/>
+      <c r="A22" s="21"/>
+      <c r="B22" s="21"/>
+      <c r="C22" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="D22" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="E22" s="20"/>
     </row>
     <row r="23" ht="18.75" customHeight="1" spans="1:5">
-      <c r="A23" s="22"/>
-      <c r="B23" s="22"/>
-      <c r="C23" s="21" t="s">
+      <c r="A23" s="21"/>
+      <c r="B23" s="21"/>
+      <c r="C23" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="D23" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="E23" s="20"/>
+    </row>
+    <row r="24" ht="18.75" customHeight="1" spans="1:5">
+      <c r="A24" s="21"/>
+      <c r="B24" s="21"/>
+      <c r="C24" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="D24" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="E24" s="20"/>
+    </row>
+    <row r="25" ht="18.75" customHeight="1" spans="1:5">
+      <c r="A25" s="21"/>
+      <c r="B25" s="21"/>
+      <c r="C25" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="D25" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="E25" s="20"/>
+    </row>
+    <row r="26" ht="18.75" customHeight="1" spans="1:5">
+      <c r="A26" s="21"/>
+      <c r="B26" s="21"/>
+      <c r="C26" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="D26" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="D23" s="21" t="s">
-        <v>61</v>
-      </c>
-      <c r="E23" s="21"/>
-    </row>
-    <row r="24" ht="18.75" customHeight="1" spans="1:5">
-      <c r="A24" s="22"/>
-      <c r="B24" s="22"/>
-      <c r="C24" s="21" t="s">
-        <v>62</v>
-      </c>
-      <c r="D24" s="21" t="s">
-        <v>61</v>
-      </c>
-      <c r="E24" s="21"/>
-    </row>
-    <row r="25" ht="18.75" customHeight="1" spans="1:5">
-      <c r="A25" s="22"/>
-      <c r="B25" s="22"/>
-      <c r="C25" s="21" t="s">
-        <v>63</v>
-      </c>
-      <c r="D25" s="21" t="s">
-        <v>64</v>
-      </c>
-      <c r="E25" s="21"/>
-    </row>
-    <row r="26" ht="18.75" customHeight="1" spans="1:5">
-      <c r="A26" s="22"/>
-      <c r="B26" s="22"/>
-      <c r="C26" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="D26" s="21" t="s">
-        <v>57</v>
-      </c>
-      <c r="E26" s="21"/>
+      <c r="E26" s="20"/>
     </row>
     <row r="27" ht="18.75" customHeight="1" spans="1:5">
-      <c r="A27" s="22"/>
-      <c r="B27" s="22"/>
-      <c r="C27" s="21" t="s">
-        <v>66</v>
-      </c>
-      <c r="D27" s="21" t="s">
+      <c r="A27" s="21"/>
+      <c r="B27" s="21"/>
+      <c r="C27" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="D27" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="E27" s="20"/>
+    </row>
+    <row r="28" ht="18.75" customHeight="1" spans="1:5">
+      <c r="A28" s="21"/>
+      <c r="B28" s="21"/>
+      <c r="C28" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="D28" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="E28" s="20"/>
+    </row>
+    <row r="29" ht="18.75" customHeight="1" spans="1:5">
+      <c r="A29" s="21"/>
+      <c r="B29" s="21"/>
+      <c r="C29" s="20" t="s">
+        <v>73</v>
+      </c>
+      <c r="D29" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="E29" s="20"/>
+    </row>
+    <row r="30" ht="18.75" customHeight="1" spans="1:5">
+      <c r="A30" s="21"/>
+      <c r="B30" s="21"/>
+      <c r="C30" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="D30" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="E30" s="20"/>
+    </row>
+    <row r="31" ht="18.75" customHeight="1" spans="1:5">
+      <c r="A31" s="22"/>
+      <c r="B31" s="22"/>
+      <c r="C31" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="D31" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="E31" s="20"/>
+    </row>
+    <row r="32" s="4" customFormat="1" ht="18.75" customHeight="1" spans="1:5">
+      <c r="A32" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="B32" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="C32" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="D32" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="E32" s="20"/>
+    </row>
+    <row r="33" ht="18.75" customHeight="1" spans="1:5">
+      <c r="A33" s="21"/>
+      <c r="B33" s="21"/>
+      <c r="C33" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="D33" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="E33" s="20"/>
+    </row>
+    <row r="34" ht="18.75" customHeight="1" spans="1:5">
+      <c r="A34" s="21"/>
+      <c r="B34" s="21"/>
+      <c r="C34" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="D34" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="E34" s="20"/>
+    </row>
+    <row r="35" ht="18.75" customHeight="1" spans="1:5">
+      <c r="A35" s="21"/>
+      <c r="B35" s="21"/>
+      <c r="C35" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="D35" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="E35" s="20"/>
+    </row>
+    <row r="36" ht="18.75" customHeight="1" spans="1:5">
+      <c r="A36" s="21"/>
+      <c r="B36" s="21"/>
+      <c r="C36" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="D36" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="E36" s="20"/>
+    </row>
+    <row r="37" ht="18.75" customHeight="1" spans="1:5">
+      <c r="A37" s="21"/>
+      <c r="B37" s="21"/>
+      <c r="C37" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="D37" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="E37" s="20"/>
+    </row>
+    <row r="38" ht="18.75" customHeight="1" spans="1:5">
+      <c r="A38" s="21"/>
+      <c r="B38" s="21"/>
+      <c r="C38" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="D38" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="E38" s="20"/>
+    </row>
+    <row r="39" ht="18.75" customHeight="1" spans="1:5">
+      <c r="A39" s="21"/>
+      <c r="B39" s="21"/>
+      <c r="C39" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="D39" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="E39" s="20"/>
+    </row>
+    <row r="40" ht="18.75" customHeight="1" spans="1:5">
+      <c r="A40" s="21"/>
+      <c r="B40" s="22"/>
+      <c r="C40" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="D40" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="E40" s="20"/>
+    </row>
+    <row r="41" ht="18.75" customHeight="1" spans="1:5">
+      <c r="A41" s="21"/>
+      <c r="B41" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="C41" s="20" t="s">
+        <v>96</v>
+      </c>
+      <c r="D41" s="20" t="s">
+        <v>97</v>
+      </c>
+      <c r="E41" s="20"/>
+    </row>
+    <row r="42" ht="18.75" customHeight="1" spans="1:5">
+      <c r="A42" s="21"/>
+      <c r="B42" s="21"/>
+      <c r="C42" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="D42" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="E42" s="20"/>
+    </row>
+    <row r="43" ht="18.75" customHeight="1" spans="1:5">
+      <c r="A43" s="21"/>
+      <c r="B43" s="21"/>
+      <c r="C43" s="20" t="s">
+        <v>100</v>
+      </c>
+      <c r="D43" s="20" t="s">
+        <v>101</v>
+      </c>
+      <c r="E43" s="20"/>
+    </row>
+    <row r="44" ht="18.75" customHeight="1" spans="1:5">
+      <c r="A44" s="21"/>
+      <c r="B44" s="21"/>
+      <c r="C44" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="D44" s="20" t="s">
+        <v>103</v>
+      </c>
+      <c r="E44" s="20"/>
+    </row>
+    <row r="45" ht="18.75" customHeight="1" spans="1:5">
+      <c r="A45" s="21"/>
+      <c r="B45" s="21"/>
+      <c r="C45" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="D45" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="E27" s="21"/>
-    </row>
-    <row r="28" ht="18.75" customHeight="1" spans="1:5">
-      <c r="A28" s="22"/>
-      <c r="B28" s="22"/>
-      <c r="C28" s="21" t="s">
-        <v>68</v>
-      </c>
-      <c r="D28" s="21" t="s">
-        <v>69</v>
-      </c>
-      <c r="E28" s="21"/>
-    </row>
-    <row r="29" ht="18.75" customHeight="1" spans="1:5">
-      <c r="A29" s="22"/>
-      <c r="B29" s="22"/>
-      <c r="C29" s="21" t="s">
-        <v>70</v>
-      </c>
-      <c r="D29" s="21" t="s">
-        <v>71</v>
-      </c>
-      <c r="E29" s="21"/>
-    </row>
-    <row r="30" ht="18.75" customHeight="1" spans="1:5">
-      <c r="A30" s="22"/>
-      <c r="B30" s="22"/>
-      <c r="C30" s="21" t="s">
-        <v>72</v>
-      </c>
-      <c r="D30" s="21" t="s">
-        <v>73</v>
-      </c>
-      <c r="E30" s="21"/>
-    </row>
-    <row r="31" ht="18.75" customHeight="1" spans="1:5">
-      <c r="A31" s="23"/>
-      <c r="B31" s="23"/>
-      <c r="C31" s="21" t="s">
-        <v>74</v>
-      </c>
-      <c r="D31" s="21" t="s">
-        <v>75</v>
-      </c>
-      <c r="E31" s="21"/>
-    </row>
-    <row r="32" s="4" customFormat="1" ht="18.75" customHeight="1" spans="1:5">
-      <c r="A32" s="20" t="s">
-        <v>76</v>
-      </c>
-      <c r="B32" s="20" t="s">
-        <v>77</v>
-      </c>
-      <c r="C32" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="D32" s="21" t="s">
-        <v>79</v>
-      </c>
-      <c r="E32" s="21"/>
-    </row>
-    <row r="33" ht="18.75" customHeight="1" spans="1:5">
-      <c r="A33" s="22"/>
-      <c r="B33" s="22"/>
-      <c r="C33" s="21" t="s">
-        <v>80</v>
-      </c>
-      <c r="D33" s="21" t="s">
-        <v>79</v>
-      </c>
-      <c r="E33" s="21"/>
-    </row>
-    <row r="34" ht="18.75" customHeight="1" spans="1:5">
-      <c r="A34" s="22"/>
-      <c r="B34" s="22"/>
-      <c r="C34" s="21" t="s">
-        <v>81</v>
-      </c>
-      <c r="D34" s="21" t="s">
-        <v>82</v>
-      </c>
-      <c r="E34" s="21"/>
-    </row>
-    <row r="35" ht="18.75" customHeight="1" spans="1:5">
-      <c r="A35" s="22"/>
-      <c r="B35" s="22"/>
-      <c r="C35" s="21" t="s">
-        <v>83</v>
-      </c>
-      <c r="D35" s="21" t="s">
-        <v>79</v>
-      </c>
-      <c r="E35" s="21"/>
-    </row>
-    <row r="36" ht="18.75" customHeight="1" spans="1:5">
-      <c r="A36" s="22"/>
-      <c r="B36" s="22"/>
-      <c r="C36" s="21" t="s">
-        <v>84</v>
-      </c>
-      <c r="D36" s="21" t="s">
-        <v>79</v>
-      </c>
-      <c r="E36" s="21"/>
-    </row>
-    <row r="37" ht="18.75" customHeight="1" spans="1:5">
-      <c r="A37" s="22"/>
-      <c r="B37" s="22"/>
-      <c r="C37" s="21" t="s">
-        <v>85</v>
-      </c>
-      <c r="D37" s="21" t="s">
-        <v>82</v>
-      </c>
-      <c r="E37" s="21"/>
-    </row>
-    <row r="38" ht="18.75" customHeight="1" spans="1:5">
-      <c r="A38" s="22"/>
-      <c r="B38" s="22"/>
-      <c r="C38" s="21" t="s">
-        <v>86</v>
-      </c>
-      <c r="D38" s="21" t="s">
-        <v>87</v>
-      </c>
-      <c r="E38" s="21"/>
-    </row>
-    <row r="39" ht="18.75" customHeight="1" spans="1:5">
-      <c r="A39" s="22"/>
-      <c r="B39" s="22"/>
-      <c r="C39" s="21" t="s">
-        <v>88</v>
-      </c>
-      <c r="D39" s="21" t="s">
-        <v>89</v>
-      </c>
-      <c r="E39" s="21"/>
-    </row>
-    <row r="40" ht="18.75" customHeight="1" spans="1:5">
-      <c r="A40" s="22"/>
-      <c r="B40" s="23"/>
-      <c r="C40" s="21" t="s">
-        <v>90</v>
-      </c>
-      <c r="D40" s="21" t="s">
-        <v>91</v>
-      </c>
-      <c r="E40" s="21"/>
-    </row>
-    <row r="41" ht="18.75" customHeight="1" spans="1:5">
-      <c r="A41" s="22"/>
-      <c r="B41" s="20" t="s">
-        <v>92</v>
-      </c>
-      <c r="C41" s="21" t="s">
-        <v>93</v>
-      </c>
-      <c r="D41" s="21" t="s">
-        <v>94</v>
-      </c>
-      <c r="E41" s="21"/>
-    </row>
-    <row r="42" ht="18.75" customHeight="1" spans="1:5">
-      <c r="A42" s="22"/>
-      <c r="B42" s="22"/>
-      <c r="C42" s="21" t="s">
-        <v>95</v>
-      </c>
-      <c r="D42" s="21" t="s">
-        <v>96</v>
-      </c>
-      <c r="E42" s="21"/>
-    </row>
-    <row r="43" ht="18.75" customHeight="1" spans="1:5">
-      <c r="A43" s="22"/>
-      <c r="B43" s="22"/>
-      <c r="C43" s="21" t="s">
+      <c r="E45" s="20"/>
+    </row>
+    <row r="46" ht="18.75" customHeight="1" spans="1:5">
+      <c r="A46" s="21"/>
+      <c r="B46" s="21"/>
+      <c r="C46" s="20" t="s">
+        <v>105</v>
+      </c>
+      <c r="D46" s="20" t="s">
+        <v>106</v>
+      </c>
+      <c r="E46" s="20"/>
+    </row>
+    <row r="47" ht="18.75" customHeight="1" spans="1:5">
+      <c r="A47" s="21"/>
+      <c r="B47" s="21"/>
+      <c r="C47" s="20" t="s">
+        <v>107</v>
+      </c>
+      <c r="D47" s="20" t="s">
         <v>97</v>
       </c>
-      <c r="D43" s="21" t="s">
-        <v>98</v>
-      </c>
-      <c r="E43" s="21"/>
-    </row>
-    <row r="44" ht="18.75" customHeight="1" spans="1:5">
-      <c r="A44" s="22"/>
-      <c r="B44" s="22"/>
-      <c r="C44" s="21" t="s">
-        <v>99</v>
-      </c>
-      <c r="D44" s="21" t="s">
-        <v>100</v>
-      </c>
-      <c r="E44" s="21"/>
-    </row>
-    <row r="45" ht="18.75" customHeight="1" spans="1:5">
-      <c r="A45" s="22"/>
-      <c r="B45" s="22"/>
-      <c r="C45" s="21" t="s">
+      <c r="E47" s="20"/>
+    </row>
+    <row r="48" ht="18.75" customHeight="1" spans="1:5">
+      <c r="A48" s="21"/>
+      <c r="B48" s="21"/>
+      <c r="C48" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="D48" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="D45" s="21" t="s">
-        <v>64</v>
-      </c>
-      <c r="E45" s="21"/>
-    </row>
-    <row r="46" ht="18.75" customHeight="1" spans="1:5">
-      <c r="A46" s="22"/>
-      <c r="B46" s="22"/>
-      <c r="C46" s="21" t="s">
-        <v>102</v>
-      </c>
-      <c r="D46" s="21" t="s">
-        <v>103</v>
-      </c>
-      <c r="E46" s="21"/>
-    </row>
-    <row r="47" ht="18.75" customHeight="1" spans="1:5">
-      <c r="A47" s="22"/>
-      <c r="B47" s="22"/>
-      <c r="C47" s="21" t="s">
-        <v>104</v>
-      </c>
-      <c r="D47" s="21" t="s">
-        <v>94</v>
-      </c>
-      <c r="E47" s="21"/>
-    </row>
-    <row r="48" ht="18.75" customHeight="1" spans="1:5">
-      <c r="A48" s="22"/>
-      <c r="B48" s="22"/>
-      <c r="C48" s="21" t="s">
-        <v>105</v>
-      </c>
-      <c r="D48" s="21" t="s">
-        <v>98</v>
-      </c>
-      <c r="E48" s="21"/>
+      <c r="E48" s="20"/>
     </row>
     <row r="49" ht="18.75" customHeight="1" spans="1:5">
-      <c r="A49" s="22"/>
-      <c r="B49" s="22"/>
-      <c r="C49" s="21" t="s">
-        <v>106</v>
-      </c>
-      <c r="D49" s="21" t="s">
-        <v>94</v>
-      </c>
-      <c r="E49" s="21"/>
+      <c r="A49" s="21"/>
+      <c r="B49" s="21"/>
+      <c r="C49" s="20" t="s">
+        <v>109</v>
+      </c>
+      <c r="D49" s="20" t="s">
+        <v>97</v>
+      </c>
+      <c r="E49" s="20"/>
     </row>
     <row r="50" ht="18.75" customHeight="1" spans="1:5">
-      <c r="A50" s="23"/>
-      <c r="B50" s="23"/>
-      <c r="C50" s="21" t="s">
-        <v>107</v>
-      </c>
-      <c r="D50" s="21" t="s">
-        <v>108</v>
-      </c>
-      <c r="E50" s="21"/>
+      <c r="A50" s="22"/>
+      <c r="B50" s="22"/>
+      <c r="C50" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="D50" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="E50" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -3281,131 +3278,131 @@
   <dimension ref="A1:T33"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="10.0083333333333" style="18" customWidth="1"/>
-    <col min="2" max="2" width="26.0083333333333" style="18" customWidth="1"/>
-    <col min="3" max="3" width="10.0083333333333" style="18" customWidth="1"/>
-    <col min="4" max="5" width="26.0083333333333" style="18" customWidth="1"/>
-    <col min="6" max="6" width="16.0083333333333" style="18" customWidth="1"/>
-    <col min="7" max="8" width="8.00833333333333" style="18" customWidth="1"/>
-    <col min="9" max="10" width="10.0083333333333" style="18" customWidth="1"/>
-    <col min="11" max="12" width="12.0083333333333" style="18" customWidth="1"/>
-    <col min="13" max="13" width="10.0083333333333" style="18" customWidth="1"/>
-    <col min="14" max="17" width="12.0083333333333" style="18" customWidth="1"/>
-    <col min="18" max="18" width="30.0083333333333" style="18" customWidth="1"/>
+    <col min="1" max="1" width="10.0083333333333" customWidth="1"/>
+    <col min="2" max="2" width="26.0083333333333" customWidth="1"/>
+    <col min="3" max="3" width="10.0083333333333" customWidth="1"/>
+    <col min="4" max="5" width="26.0083333333333" customWidth="1"/>
+    <col min="6" max="6" width="16.0083333333333" customWidth="1"/>
+    <col min="7" max="8" width="8.00833333333333" customWidth="1"/>
+    <col min="9" max="10" width="10.0083333333333" customWidth="1"/>
+    <col min="11" max="12" width="12.0083333333333" customWidth="1"/>
+    <col min="13" max="13" width="10.0083333333333" customWidth="1"/>
+    <col min="14" max="17" width="12.0083333333333" customWidth="1"/>
+    <col min="18" max="18" width="30.0083333333333" customWidth="1"/>
     <col min="19" max="20" width="13.575" style="4" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.75" customHeight="1" spans="1:20">
       <c r="A1" s="13" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="S1" s="16"/>
       <c r="T1" s="16"/>
     </row>
     <row r="2" s="4" customFormat="1" ht="30" customHeight="1" spans="1:20">
       <c r="A2" s="9" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="M2" s="9" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="O2" s="9" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="P2" s="9" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="Q2" s="9" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="R2" s="9" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="S2" s="17"/>
       <c r="T2" s="17"/>
     </row>
     <row r="3" ht="18.75" customHeight="1" spans="1:20">
       <c r="A3" s="11" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="E3" s="11"/>
       <c r="F3" s="11" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="G3" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="H3" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="I3" s="11" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="J3" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="K3" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="L3" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="M3" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="N3" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="O3" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="P3" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="Q3" s="11"/>
       <c r="R3" s="11"/>
@@ -3414,50 +3411,50 @@
     </row>
     <row r="4" ht="18.75" customHeight="1" spans="1:20">
       <c r="A4" s="11" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="E4" s="11"/>
       <c r="F4" s="11" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="I4" s="11" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="K4" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="L4" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="M4" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="N4" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="O4" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="P4" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="Q4" s="11"/>
       <c r="R4" s="11"/>
@@ -3466,50 +3463,50 @@
     </row>
     <row r="5" ht="18.75" customHeight="1" spans="1:20">
       <c r="A5" s="11" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E5" s="11"/>
       <c r="F5" s="11" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="I5" s="11" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="J5" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="K5" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="L5" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="M5" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="N5" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="O5" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="P5" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="Q5" s="11"/>
       <c r="R5" s="11"/>
@@ -3518,52 +3515,52 @@
     </row>
     <row r="6" ht="18.75" customHeight="1" spans="1:20">
       <c r="A6" s="11" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="I6" s="11" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="J6" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="K6" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="L6" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="M6" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="N6" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="O6" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="P6" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="Q6" s="11"/>
       <c r="R6" s="11"/>
@@ -3572,52 +3569,52 @@
     </row>
     <row r="7" ht="18.75" customHeight="1" spans="1:20">
       <c r="A7" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="C7" s="11" t="s">
         <v>138</v>
       </c>
-      <c r="B7" s="11" t="s">
-        <v>139</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>135</v>
-      </c>
       <c r="D7" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="E7" s="11" t="s">
         <v>144</v>
       </c>
-      <c r="E7" s="11" t="s">
-        <v>141</v>
-      </c>
       <c r="F7" s="11" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="I7" s="11" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="J7" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="K7" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="L7" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="M7" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="N7" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="O7" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="P7" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="Q7" s="11"/>
       <c r="R7" s="11"/>
@@ -3626,48 +3623,48 @@
     </row>
     <row r="8" ht="18.75" customHeight="1" spans="1:20">
       <c r="A8" s="11" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D8" s="11"/>
       <c r="E8" s="11"/>
       <c r="F8" s="11" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="I8" s="11" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="J8" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="K8" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="L8" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="M8" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="N8" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="O8" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="P8" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="Q8" s="11"/>
       <c r="R8" s="11"/>
@@ -3676,50 +3673,50 @@
     </row>
     <row r="9" ht="18.75" customHeight="1" spans="1:20">
       <c r="A9" s="11" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="E9" s="11"/>
       <c r="F9" s="11" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="H9" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="I9" s="11" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="J9" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="K9" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="L9" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="M9" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="N9" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="O9" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="P9" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="Q9" s="11"/>
       <c r="R9" s="11"/>
@@ -3728,50 +3725,50 @@
     </row>
     <row r="10" ht="18.75" customHeight="1" spans="1:20">
       <c r="A10" s="11" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="E10" s="11"/>
       <c r="F10" s="11" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="I10" s="11" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="J10" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="K10" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="L10" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="M10" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="N10" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="O10" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="P10" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="Q10" s="11"/>
       <c r="R10" s="11"/>
@@ -3780,50 +3777,50 @@
     </row>
     <row r="11" ht="18.75" customHeight="1" spans="1:20">
       <c r="A11" s="11" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="E11" s="11"/>
       <c r="F11" s="11" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="H11" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="I11" s="11" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="J11" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="K11" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="L11" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="M11" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="N11" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="O11" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="P11" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="Q11" s="11"/>
       <c r="R11" s="11"/>
@@ -3832,50 +3829,50 @@
     </row>
     <row r="12" ht="18.75" customHeight="1" spans="1:20">
       <c r="A12" s="11" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="E12" s="11"/>
       <c r="F12" s="11" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="I12" s="11" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="J12" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="K12" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="L12" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="M12" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="N12" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="O12" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="P12" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="Q12" s="11"/>
       <c r="R12" s="11"/>
@@ -3884,50 +3881,50 @@
     </row>
     <row r="13" ht="18.75" customHeight="1" spans="1:20">
       <c r="A13" s="11" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="E13" s="11"/>
       <c r="F13" s="11" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="I13" s="11" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="J13" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="K13" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="L13" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="M13" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="N13" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="O13" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="P13" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="Q13" s="11"/>
       <c r="R13" s="11"/>
@@ -3936,50 +3933,50 @@
     </row>
     <row r="14" ht="18.75" customHeight="1" spans="1:20">
       <c r="A14" s="11" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D14" s="11"/>
       <c r="E14" s="11" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="I14" s="11" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="J14" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="K14" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="L14" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="M14" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="N14" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="O14" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="P14" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="Q14" s="11"/>
       <c r="R14" s="11"/>
@@ -3988,50 +3985,50 @@
     </row>
     <row r="15" ht="18.75" customHeight="1" spans="1:20">
       <c r="A15" s="11" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="E15" s="11"/>
       <c r="F15" s="11" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="G15" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="H15" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="I15" s="11" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="J15" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="K15" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="L15" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="M15" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="N15" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="O15" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="P15" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="Q15" s="11"/>
       <c r="R15" s="11"/>
@@ -4040,50 +4037,50 @@
     </row>
     <row r="16" ht="18.75" customHeight="1" spans="1:20">
       <c r="A16" s="11" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="E16" s="11"/>
       <c r="F16" s="11" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="H16" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="I16" s="11" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="J16" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="K16" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="L16" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="M16" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="N16" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="O16" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="P16" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="Q16" s="11"/>
       <c r="R16" s="11"/>
@@ -4092,50 +4089,50 @@
     </row>
     <row r="17" ht="18.75" customHeight="1" spans="1:20">
       <c r="A17" s="11" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="E17" s="11"/>
       <c r="F17" s="11" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="G17" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="H17" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="I17" s="11" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="J17" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="K17" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="L17" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="M17" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="N17" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="O17" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="P17" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="Q17" s="11"/>
       <c r="R17" s="11"/>
@@ -4144,50 +4141,50 @@
     </row>
     <row r="18" ht="18.75" customHeight="1" spans="1:20">
       <c r="A18" s="11" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="E18" s="11"/>
       <c r="F18" s="11" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="I18" s="11" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="J18" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="K18" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="L18" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="M18" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="N18" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="O18" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="P18" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="Q18" s="11"/>
       <c r="R18" s="11"/>
@@ -4196,158 +4193,158 @@
     </row>
     <row r="19" ht="18.75" customHeight="1" spans="1:20">
       <c r="A19" s="11" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="E19" s="11"/>
       <c r="F19" s="11" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="G19" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="H19" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="I19" s="11" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="J19" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="K19" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="L19" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="M19" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="N19" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="O19" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="P19" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="Q19" s="11"/>
       <c r="R19" s="11" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="S19" s="16"/>
       <c r="T19" s="16"/>
     </row>
     <row r="20" ht="18.75" customHeight="1" spans="1:20">
       <c r="A20" s="11" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="E20" s="11"/>
       <c r="F20" s="11" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="G20" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="H20" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="I20" s="11" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="J20" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="K20" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="L20" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="M20" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="N20" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="O20" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="P20" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="Q20" s="11"/>
       <c r="R20" s="11" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="S20" s="16"/>
       <c r="T20" s="16"/>
     </row>
     <row r="21" ht="18.75" customHeight="1" spans="1:20">
       <c r="A21" s="11" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="E21" s="11"/>
       <c r="F21" s="11" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="G21" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="H21" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="I21" s="11" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="J21" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="K21" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="L21" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="M21" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="N21" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="O21" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="P21" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="Q21" s="11"/>
       <c r="R21" s="11"/>
@@ -4356,50 +4353,50 @@
     </row>
     <row r="22" ht="18.75" customHeight="1" spans="1:20">
       <c r="A22" s="11" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="E22" s="11"/>
       <c r="F22" s="11" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="G22" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="H22" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="I22" s="11" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="J22" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="K22" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="L22" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="M22" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="N22" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="O22" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="P22" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="Q22" s="11"/>
       <c r="R22" s="11"/>
@@ -4408,50 +4405,50 @@
     </row>
     <row r="23" ht="18.75" customHeight="1" spans="1:20">
       <c r="A23" s="11" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="E23" s="11"/>
       <c r="F23" s="11" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="G23" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="H23" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="I23" s="11" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="J23" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="K23" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="L23" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="M23" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="N23" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="O23" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="P23" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="Q23" s="11"/>
       <c r="R23" s="11"/>
@@ -4460,50 +4457,50 @@
     </row>
     <row r="24" ht="18.75" customHeight="1" spans="1:20">
       <c r="A24" s="11" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D24" s="11"/>
       <c r="E24" s="11" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="G24" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="H24" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="I24" s="11" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="J24" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="K24" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="L24" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="M24" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="N24" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="O24" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="P24" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="Q24" s="11"/>
       <c r="R24" s="11"/>
@@ -4512,52 +4509,52 @@
     </row>
     <row r="25" ht="18.75" customHeight="1" spans="1:20">
       <c r="A25" s="11" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E25" s="11" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="G25" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="H25" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="I25" s="11" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="J25" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="K25" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="L25" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="M25" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="N25" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="O25" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="P25" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="Q25" s="11"/>
       <c r="R25" s="11"/>
@@ -4566,52 +4563,52 @@
     </row>
     <row r="26" ht="18.75" customHeight="1" spans="1:20">
       <c r="A26" s="11" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="G26" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="H26" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="I26" s="11" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="J26" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="K26" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="L26" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="M26" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="N26" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="O26" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="P26" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="Q26" s="11"/>
       <c r="R26" s="11"/>
@@ -4620,52 +4617,52 @@
     </row>
     <row r="27" ht="18.75" customHeight="1" spans="1:20">
       <c r="A27" s="11" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="D27" s="11" t="s">
+        <v>197</v>
+      </c>
+      <c r="E27" s="11" t="s">
         <v>194</v>
       </c>
-      <c r="E27" s="11" t="s">
-        <v>191</v>
-      </c>
       <c r="F27" s="11" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="G27" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="H27" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="I27" s="11" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="J27" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="K27" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="L27" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="M27" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="N27" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="O27" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="P27" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="Q27" s="11"/>
       <c r="R27" s="11"/>
@@ -4674,206 +4671,206 @@
     </row>
     <row r="28" ht="20.25" customHeight="1" spans="1:20">
       <c r="A28" s="11" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D28" s="11"/>
       <c r="E28" s="11"/>
       <c r="F28" s="11" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="G28" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="H28" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="I28" s="11" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="J28" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="K28" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="L28" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="M28" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="N28" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="O28" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="P28" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="Q28" s="11"/>
       <c r="R28" s="11" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="S28" s="16"/>
       <c r="T28" s="16"/>
     </row>
     <row r="29" ht="20.25" customHeight="1" spans="1:20">
       <c r="A29" s="11" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D29" s="11"/>
       <c r="E29" s="11"/>
       <c r="F29" s="11" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="G29" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="H29" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="I29" s="11" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="J29" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="K29" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="L29" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="M29" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="N29" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="O29" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="P29" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="Q29" s="11"/>
       <c r="R29" s="11" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="S29" s="16"/>
       <c r="T29" s="16"/>
     </row>
     <row r="30" ht="20.25" customHeight="1" spans="1:20">
       <c r="A30" s="11" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D30" s="11"/>
       <c r="E30" s="11"/>
       <c r="F30" s="11" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="G30" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="H30" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="I30" s="11" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="J30" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="K30" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="L30" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="M30" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="N30" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="O30" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="P30" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="Q30" s="11"/>
       <c r="R30" s="11" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="S30" s="16"/>
       <c r="T30" s="16"/>
     </row>
     <row r="31" ht="18.75" customHeight="1" spans="1:20">
       <c r="A31" s="11" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="E31" s="11"/>
       <c r="F31" s="11" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="G31" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="H31" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="I31" s="11" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="J31" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="K31" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="L31" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="M31" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="N31" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="O31" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="P31" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="Q31" s="11"/>
       <c r="R31" s="11"/>
@@ -4882,50 +4879,50 @@
     </row>
     <row r="32" ht="18.75" customHeight="1" spans="1:20">
       <c r="A32" s="11" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D32" s="11" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="E32" s="11"/>
       <c r="F32" s="11" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="G32" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="H32" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="I32" s="11" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="J32" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="K32" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="L32" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="M32" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="N32" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="O32" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="P32" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="Q32" s="11"/>
       <c r="R32" s="11"/>
@@ -4934,50 +4931,50 @@
     </row>
     <row r="33" s="4" customFormat="1" ht="18.75" customHeight="1" spans="1:20">
       <c r="A33" s="4" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="E33" s="4"/>
       <c r="F33" s="4" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="I33" s="4" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="J33" s="4" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="K33" s="4" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="L33" s="4" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="M33" s="4" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="N33" s="4" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="O33" s="4" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="P33" s="4" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="Q33" s="4"/>
       <c r="R33" s="4"/>
@@ -5017,62 +5014,62 @@
   <sheetData>
     <row r="1" ht="18.75" customHeight="1" spans="1:23">
       <c r="A1" s="13" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="V1" s="16"/>
       <c r="W1" s="16"/>
     </row>
     <row r="2" s="4" customFormat="1" ht="30" customHeight="1" spans="1:23">
       <c r="A2" s="9" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="M2" s="9" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="O2" s="9" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="P2" s="9" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="Q2" s="9" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="R2" s="17"/>
       <c r="S2" s="17"/>
@@ -5083,51 +5080,51 @@
     </row>
     <row r="3" ht="21.75" customHeight="1" spans="1:23">
       <c r="A3" s="11" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="G3" s="11"/>
       <c r="H3" s="10">
         <v>50</v>
       </c>
       <c r="I3" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="J3" s="11" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="K3" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="L3" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="M3" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="N3" s="11" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="O3" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="P3" s="11"/>
       <c r="Q3" s="11" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="R3" s="11"/>
       <c r="S3" s="11"/>
@@ -5138,51 +5135,51 @@
     </row>
     <row r="4" ht="21.75" customHeight="1" spans="1:23">
       <c r="A4" s="11" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="G4" s="11"/>
       <c r="H4" s="10">
         <v>30</v>
       </c>
       <c r="I4" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="K4" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="L4" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="M4" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="N4" s="11" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="O4" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="P4" s="11"/>
       <c r="Q4" s="11" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="R4" s="11"/>
       <c r="S4" s="11"/>
@@ -5193,51 +5190,51 @@
     </row>
     <row r="5" ht="21.75" customHeight="1" spans="1:23">
       <c r="A5" s="11" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="G5" s="11"/>
       <c r="H5" s="10">
         <v>225</v>
       </c>
       <c r="I5" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="J5" s="11" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="K5" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="L5" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="M5" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="N5" s="11" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="O5" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="P5" s="11"/>
       <c r="Q5" s="11" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="R5" s="11"/>
       <c r="S5" s="11"/>
@@ -5248,51 +5245,51 @@
     </row>
     <row r="6" ht="21.75" customHeight="1" spans="1:23">
       <c r="A6" s="11" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="G6" s="11"/>
       <c r="H6" s="10">
         <v>225</v>
       </c>
       <c r="I6" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="J6" s="11" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="K6" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="L6" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="M6" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="N6" s="11" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="O6" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="P6" s="11"/>
       <c r="Q6" s="11" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="R6" s="11"/>
       <c r="S6" s="11"/>
@@ -5303,51 +5300,51 @@
     </row>
     <row r="7" ht="21.75" customHeight="1" spans="1:23">
       <c r="A7" s="11" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="G7" s="11"/>
       <c r="H7" s="10">
         <v>225</v>
       </c>
       <c r="I7" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="J7" s="11" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="K7" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="L7" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="M7" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="N7" s="11" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="O7" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="P7" s="11"/>
       <c r="Q7" s="11" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="R7" s="11"/>
       <c r="S7" s="11"/>
@@ -5358,51 +5355,51 @@
     </row>
     <row r="8" ht="21.75" customHeight="1" spans="1:23">
       <c r="A8" s="11" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="G8" s="11"/>
       <c r="H8" s="10">
         <v>25</v>
       </c>
       <c r="I8" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="J8" s="11" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="K8" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="L8" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="M8" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="N8" s="11" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="O8" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="P8" s="11"/>
       <c r="Q8" s="11" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="R8" s="11"/>
       <c r="S8" s="11"/>
@@ -5413,51 +5410,51 @@
     </row>
     <row r="9" ht="21.75" customHeight="1" spans="1:23">
       <c r="A9" s="11" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="G9" s="11"/>
       <c r="H9" s="10">
         <v>32</v>
       </c>
       <c r="I9" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="J9" s="11" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="K9" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="L9" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="M9" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="N9" s="11" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="O9" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="P9" s="11"/>
       <c r="Q9" s="11" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="R9" s="11"/>
       <c r="S9" s="11"/>
@@ -5468,53 +5465,53 @@
     </row>
     <row r="10" ht="21.75" customHeight="1" spans="1:23">
       <c r="A10" s="11" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="H10" s="10">
         <v>26</v>
       </c>
       <c r="I10" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="J10" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="K10" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="L10" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="M10" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="N10" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="O10" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="P10" s="11"/>
       <c r="Q10" s="11" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="R10" s="11"/>
       <c r="S10" s="11"/>
@@ -5525,53 +5522,53 @@
     </row>
     <row r="11" ht="21.75" customHeight="1" spans="1:23">
       <c r="A11" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>252</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>226</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>227</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>247</v>
+      </c>
+      <c r="F11" s="11" t="s">
         <v>248</v>
       </c>
-      <c r="B11" s="11" t="s">
-        <v>249</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>223</v>
-      </c>
-      <c r="D11" s="11" t="s">
-        <v>224</v>
-      </c>
-      <c r="E11" s="11" t="s">
-        <v>244</v>
-      </c>
-      <c r="F11" s="11" t="s">
-        <v>245</v>
-      </c>
       <c r="G11" s="11" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="H11" s="10">
         <v>3</v>
       </c>
       <c r="I11" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="J11" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="K11" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="L11" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="M11" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="N11" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="O11" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="P11" s="11"/>
       <c r="Q11" s="11" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="R11" s="11"/>
       <c r="S11" s="11"/>
@@ -5582,53 +5579,53 @@
     </row>
     <row r="12" ht="21.75" customHeight="1" spans="1:23">
       <c r="A12" s="11" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="H12" s="10">
         <v>11</v>
       </c>
       <c r="I12" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="J12" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="K12" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="L12" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="M12" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="N12" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="O12" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="P12" s="11"/>
       <c r="Q12" s="11" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="R12" s="11"/>
       <c r="S12" s="11"/>
@@ -5639,51 +5636,51 @@
     </row>
     <row r="13" ht="21.75" customHeight="1" spans="1:23">
       <c r="A13" s="11" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="G13" s="11"/>
       <c r="H13" s="10">
         <v>10</v>
       </c>
       <c r="I13" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="J13" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="K13" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="L13" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="M13" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="N13" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="O13" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="P13" s="11"/>
       <c r="Q13" s="11" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="R13" s="11"/>
       <c r="S13" s="11"/>
@@ -5694,53 +5691,53 @@
     </row>
     <row r="14" ht="21.75" customHeight="1" spans="1:23">
       <c r="A14" s="11" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="H14" s="10">
         <v>4</v>
       </c>
       <c r="I14" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="J14" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="K14" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="L14" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="M14" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="N14" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="O14" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="P14" s="11"/>
       <c r="Q14" s="11" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="R14" s="11"/>
       <c r="S14" s="11"/>
@@ -5751,49 +5748,49 @@
     </row>
     <row r="15" ht="19.5" customHeight="1" spans="1:23">
       <c r="A15" s="11" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="G15" s="11" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="H15" s="10">
         <v>11</v>
       </c>
       <c r="I15" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="J15" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="K15" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="L15" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="M15" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="N15" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="O15" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="P15" s="11"/>
       <c r="Q15" s="11"/>
@@ -5806,53 +5803,53 @@
     </row>
     <row r="16" ht="21.75" customHeight="1" spans="1:23">
       <c r="A16" s="11" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="H16" s="10">
         <v>13</v>
       </c>
       <c r="I16" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="J16" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="K16" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="L16" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="M16" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="N16" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="O16" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="P16" s="11"/>
       <c r="Q16" s="11" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="R16" s="11"/>
       <c r="S16" s="11"/>
@@ -5863,53 +5860,53 @@
     </row>
     <row r="17" ht="21.75" customHeight="1" spans="1:23">
       <c r="A17" s="11" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="G17" s="11" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="H17" s="10">
         <v>3</v>
       </c>
       <c r="I17" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="J17" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="K17" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="L17" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="M17" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="N17" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="O17" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="P17" s="11"/>
       <c r="Q17" s="11" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="R17" s="11"/>
       <c r="S17" s="11"/>
@@ -5920,53 +5917,53 @@
     </row>
     <row r="18" ht="21.75" customHeight="1" spans="1:23">
       <c r="A18" s="11" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="H18" s="10">
         <v>5</v>
       </c>
       <c r="I18" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="J18" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="K18" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="L18" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="M18" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="N18" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="O18" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="P18" s="11"/>
       <c r="Q18" s="11" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="R18" s="11"/>
       <c r="S18" s="11"/>
@@ -5977,51 +5974,51 @@
     </row>
     <row r="19" ht="21.75" customHeight="1" spans="1:23">
       <c r="A19" s="11" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="G19" s="11"/>
       <c r="H19" s="10">
         <v>1</v>
       </c>
       <c r="I19" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="J19" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="K19" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="L19" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="M19" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="N19" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="O19" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="P19" s="11"/>
       <c r="Q19" s="11" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="R19" s="11"/>
       <c r="S19" s="11"/>
@@ -6032,53 +6029,53 @@
     </row>
     <row r="20" ht="21.75" customHeight="1" spans="1:23">
       <c r="A20" s="11" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="G20" s="11" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="H20" s="10">
         <v>17</v>
       </c>
       <c r="I20" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="J20" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="K20" s="11" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="L20" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="M20" s="11" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="N20" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="O20" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="P20" s="11"/>
       <c r="Q20" s="11" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="R20" s="11"/>
       <c r="S20" s="11"/>
@@ -6089,51 +6086,51 @@
     </row>
     <row r="21" ht="21.75" customHeight="1" spans="1:23">
       <c r="A21" s="11" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="G21" s="11"/>
       <c r="H21" s="10">
         <v>9</v>
       </c>
       <c r="I21" s="11" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="J21" s="11" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="K21" s="11" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="L21" s="11" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="M21" s="11" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="N21" s="11" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="O21" s="11" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="P21" s="11"/>
       <c r="Q21" s="11" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="R21" s="11"/>
       <c r="S21" s="11"/>
@@ -6144,51 +6141,51 @@
     </row>
     <row r="22" ht="21.75" customHeight="1" spans="1:23">
       <c r="A22" s="11" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="E22" s="11" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="G22" s="11"/>
       <c r="H22" s="10">
         <v>20</v>
       </c>
       <c r="I22" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="J22" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="K22" s="11" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="L22" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="M22" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="N22" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="O22" s="11" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="P22" s="11"/>
       <c r="Q22" s="11" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="R22" s="11"/>
       <c r="S22" s="11"/>
@@ -6199,51 +6196,51 @@
     </row>
     <row r="23" ht="21.75" customHeight="1" spans="1:23">
       <c r="A23" s="11" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E23" s="11" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="G23" s="11"/>
       <c r="H23" s="10">
         <v>32</v>
       </c>
       <c r="I23" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="J23" s="11" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="K23" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="L23" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="M23" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="N23" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="O23" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="P23" s="11"/>
       <c r="Q23" s="11" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="R23" s="11"/>
       <c r="S23" s="11"/>
@@ -6254,51 +6251,51 @@
     </row>
     <row r="24" ht="21.75" customHeight="1" spans="1:23">
       <c r="A24" s="11" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="E24" s="11" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="G24" s="11"/>
       <c r="H24" s="10">
         <v>11</v>
       </c>
       <c r="I24" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="J24" s="11" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="K24" s="11" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="L24" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="M24" s="11" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="N24" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="O24" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="P24" s="11"/>
       <c r="Q24" s="11" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="R24" s="11"/>
       <c r="S24" s="11"/>
@@ -6309,49 +6306,49 @@
     </row>
     <row r="25" ht="19.5" customHeight="1" spans="1:23">
       <c r="A25" s="11" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E25" s="11" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="G25" s="11" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="H25" s="12">
         <v>4</v>
       </c>
       <c r="I25" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="J25" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="K25" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="L25" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="M25" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="N25" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="O25" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="P25" s="11"/>
       <c r="Q25" s="11"/>
@@ -6364,49 +6361,49 @@
     </row>
     <row r="26" ht="19.5" customHeight="1" spans="1:23">
       <c r="A26" s="11" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="G26" s="11" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H26" s="12">
         <v>4</v>
       </c>
       <c r="I26" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="J26" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="K26" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="L26" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="M26" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="N26" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="O26" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="P26" s="11"/>
       <c r="Q26" s="11"/>
@@ -6419,49 +6416,49 @@
     </row>
     <row r="27" ht="19.5" customHeight="1" spans="1:23">
       <c r="A27" s="11" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="F27" s="11" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="G27" s="11" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="H27" s="12">
         <v>4</v>
       </c>
       <c r="I27" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="J27" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="K27" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="L27" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="M27" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="N27" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="O27" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="P27" s="11"/>
       <c r="Q27" s="11"/>
@@ -6474,53 +6471,53 @@
     </row>
     <row r="28" ht="21.75" customHeight="1" spans="1:23">
       <c r="A28" s="11" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E28" s="11" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="F28" s="11" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="G28" s="11" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="H28" s="12">
         <v>48</v>
       </c>
       <c r="I28" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="J28" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="K28" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="L28" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="M28" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="N28" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="O28" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="P28" s="11"/>
       <c r="Q28" s="11" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="R28" s="11"/>
       <c r="S28" s="11"/>
@@ -6531,49 +6528,49 @@
     </row>
     <row r="29" ht="19.5" customHeight="1" spans="1:23">
       <c r="A29" s="11" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E29" s="11" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="F29" s="11" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="G29" s="11" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="H29" s="12">
         <v>4</v>
       </c>
       <c r="I29" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="J29" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="K29" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="L29" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="M29" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="N29" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="O29" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="P29" s="11"/>
       <c r="Q29" s="11"/>
@@ -6586,53 +6583,53 @@
     </row>
     <row r="30" ht="21.75" customHeight="1" spans="1:23">
       <c r="A30" s="11" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="F30" s="11" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="G30" s="11" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="H30" s="12">
         <v>1</v>
       </c>
       <c r="I30" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="J30" s="11" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="K30" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="L30" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="M30" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="N30" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="O30" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="P30" s="11"/>
       <c r="Q30" s="11" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="R30" s="11"/>
       <c r="S30" s="11"/>
@@ -6643,49 +6640,49 @@
     </row>
     <row r="31" ht="19.5" customHeight="1" spans="1:23">
       <c r="A31" s="11" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="F31" s="11" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="G31" s="11" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="H31" s="12">
         <v>4</v>
       </c>
       <c r="I31" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="J31" s="11" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="K31" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="L31" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="M31" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="N31" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="O31" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="P31" s="11"/>
       <c r="Q31" s="11"/>
@@ -6753,7 +6750,7 @@
   <sheetData>
     <row r="1" ht="18.75" customHeight="1" spans="1:20">
       <c r="A1" s="13" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="Q1" s="6"/>
       <c r="R1" s="6"/>
@@ -6762,52 +6759,52 @@
     </row>
     <row r="2" s="4" customFormat="1" ht="30" customHeight="1" spans="1:20">
       <c r="A2" s="14" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="E2" s="14" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="F2" s="14" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="G2" s="14" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="H2" s="14" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="I2" s="14" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="J2" s="14" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="K2" s="14" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="L2" s="14" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="M2" s="14" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="N2" s="14" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="O2" s="14" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="P2" s="14" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="Q2" s="15"/>
       <c r="R2" s="15"/>
@@ -6816,50 +6813,50 @@
     </row>
     <row r="3" ht="18.75" customHeight="1" spans="1:20">
       <c r="A3" s="11" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="E3" s="11">
         <v>1</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="G3" s="11">
         <v>2</v>
       </c>
       <c r="H3" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="I3" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="J3" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="K3" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="L3" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="M3" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="N3" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="O3" s="11"/>
       <c r="P3" s="11" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="Q3" s="11"/>
       <c r="R3" s="11"/>
@@ -6868,50 +6865,50 @@
     </row>
     <row r="4" ht="18.75" customHeight="1" spans="1:20">
       <c r="A4" s="11" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="E4" s="11">
         <v>0</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="G4" s="11">
         <v>2</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="I4" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="K4" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="L4" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="M4" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="N4" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="O4" s="11"/>
       <c r="P4" s="11" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="Q4" s="11"/>
       <c r="R4" s="11"/>
@@ -6920,46 +6917,46 @@
     </row>
     <row r="5" ht="18.75" customHeight="1" spans="1:20">
       <c r="A5" s="11" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="E5" s="11">
         <v>1</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="G5" s="11">
         <v>2</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="I5" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="J5" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="K5" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="L5" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="M5" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="N5" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="O5" s="11"/>
       <c r="P5" s="11"/>
@@ -6970,50 +6967,50 @@
     </row>
     <row r="6" ht="18.75" customHeight="1" spans="1:20">
       <c r="A6" s="11" t="s">
+        <v>342</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>343</v>
+      </c>
+      <c r="C6" s="11" t="s">
         <v>339</v>
       </c>
-      <c r="B6" s="11" t="s">
-        <v>340</v>
-      </c>
-      <c r="C6" s="11" t="s">
-        <v>336</v>
-      </c>
       <c r="D6" s="11" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="E6" s="11">
         <v>0</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="G6" s="11">
         <v>2</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="I6" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="J6" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="K6" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="L6" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="M6" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="N6" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="O6" s="11"/>
       <c r="P6" s="11" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="Q6" s="11"/>
       <c r="R6" s="11"/>
@@ -7630,42 +7627,42 @@
   <sheetData>
     <row r="1" ht="18.75" customHeight="1" spans="1:11">
       <c r="A1" s="7" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="2" s="4" customFormat="1" ht="30" customHeight="1" spans="1:11">
       <c r="A2" s="8" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="3" ht="18.75" customHeight="1" spans="1:11">
@@ -7673,30 +7670,30 @@
         <v>1</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="C3" s="10">
         <v>17</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="F3" s="11"/>
       <c r="G3" s="11" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="H3" s="11" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="I3" s="11"/>
       <c r="J3" s="11" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="K3" s="11" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="4" ht="18.75" customHeight="1" spans="1:11">
@@ -7704,28 +7701,28 @@
         <v>2</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="C4" s="10">
         <v>20</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="F4" s="11"/>
       <c r="G4" s="11" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="H4" s="11"/>
       <c r="I4" s="11"/>
       <c r="J4" s="11" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="K4" s="11" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="5" ht="18.75" customHeight="1" spans="1:11">
@@ -7733,28 +7730,28 @@
         <v>3</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="C5" s="10">
         <v>9</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="F5" s="11"/>
       <c r="G5" s="11" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="H5" s="11"/>
       <c r="I5" s="11"/>
       <c r="J5" s="11" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="K5" s="11" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="6" ht="18.75" customHeight="1" spans="1:11">
@@ -7762,28 +7759,28 @@
         <v>4</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="C6" s="10">
         <v>10</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="F6" s="11"/>
       <c r="G6" s="11" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="H6" s="11"/>
       <c r="I6" s="11"/>
       <c r="J6" s="11" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="K6" s="11" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="7" ht="18.75" customHeight="1" spans="1:11">
@@ -7791,28 +7788,28 @@
         <v>5</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="C7" s="10">
         <v>11</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="F7" s="11"/>
       <c r="G7" s="11" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="H7" s="11"/>
       <c r="I7" s="11"/>
       <c r="J7" s="11" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="K7" s="11" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="8" ht="18.75" customHeight="1" spans="1:11">
@@ -8158,69 +8155,69 @@
     <col min="1" max="17" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40.5" spans="1:17">
+    <row r="1" ht="40.5" customHeight="1" spans="1:17">
       <c r="A1" s="1" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="2" spans="1:17">
       <c r="A2" s="2" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="E2" s="2">
         <v>10</v>
@@ -8228,14 +8225,12 @@
       <c r="F2" s="2">
         <v>10</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>382</v>
-      </c>
+      <c r="G2" s="2"/>
       <c r="H2" s="2" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I2" s="2">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="J2" s="2">
         <v>9</v>
@@ -8244,13 +8239,11 @@
         <v>3</v>
       </c>
       <c r="L2" s="2">
-        <v>2</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>384</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="M2" s="2"/>
       <c r="N2" s="2" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="O2" s="2">
         <v>0</v>
@@ -8260,14 +8253,14 @@
     </row>
     <row r="3" spans="1:17">
       <c r="A3" s="3" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B3" s="3"/>
-      <c r="C3" s="3" t="b">
-        <v>1</v>
+      <c r="C3" s="2" t="b">
+        <v>0</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E3" s="3">
         <v>10</v>
@@ -8275,29 +8268,25 @@
       <c r="F3" s="3">
         <v>10</v>
       </c>
-      <c r="G3" s="3" t="s">
-        <v>388</v>
-      </c>
+      <c r="G3" s="3"/>
       <c r="H3" s="3" t="s">
         <v>389</v>
       </c>
       <c r="I3" s="3">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="J3" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K3" s="3">
         <v>3</v>
       </c>
       <c r="L3" s="3">
-        <v>2</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>390</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="M3" s="3"/>
       <c r="N3" s="3" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="O3" s="3">
         <v>0</v>
@@ -8307,7 +8296,7 @@
     </row>
     <row r="4" spans="1:17">
       <c r="A4" s="2" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B4" s="2">
         <v>16</v>
@@ -8316,7 +8305,7 @@
         <v>0</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E4" s="2">
         <v>10</v>
@@ -8326,7 +8315,7 @@
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="2" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="I4" s="2">
         <v>16</v>
@@ -8342,7 +8331,7 @@
       </c>
       <c r="M4" s="2"/>
       <c r="N4" s="2" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="O4" s="2">
         <v>0</v>
@@ -8366,29 +8355,29 @@
     <col min="5" max="5" width="34.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27" spans="1:5">
+    <row r="1" ht="27" customHeight="1" spans="1:5">
       <c r="A1" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>397</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>398</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>399</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>400</v>
       </c>
       <c r="C2" s="2">
         <v>1</v>
@@ -8402,10 +8391,10 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="3" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C3" s="3">
         <v>2</v>
@@ -8419,10 +8408,10 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C4" s="2">
         <v>3</v>
